--- a/260830.xlsx
+++ b/260830.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C79D05-D3CA-4841-9EBD-667B42CDB480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDDFBBC-90C7-4D0F-A785-D1D7C850471D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5960" yWindow="3610" windowWidth="15030" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10280" yWindow="4110" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,17 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Küpper: Dann wenden wir uns mal den Leuten zu, die sozusagen hier zugewiesen sind, Stichwort """""""" Integration"""""""" .
-Köln ist ja eine sehr christlich geprägte Stadt, also mit sehr, sehr offenen Armen.
-müssen wir sie immer wieder einfordern.
-Es gibt auch die ewig Gestrigen, die das überhaupt nicht verstehen, dass unsere Gesellschaft sich wandeln wird.
-Aber ich bin von den Kölnern ganz und gar überzeugt, ich bin sogar stolz darauf,  und ein hohes ehrenamtliches Engagement zeigen auf Dauer bei der Unterbringung von Flüchtlingen, also eine echte Willkommenskultur.
-Küpper: sie aus der Türkei gesteuert wird.
-Die DITIB ist im Stadtbild ja auch sehr präsent durch diese große Moschee, den großen Moscheebau, der allerdings seit Jahren auf seine Fertigstellung wartet.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>indem wir die Länderstaatsanwaltschaften noch enger an uns heranbinden.
 Und insoweit berichten uns die Länder sehr frühzeitig.
@@ -60,6 +50,15 @@
 Ich glaube, dass alle sehr betrübt darüber sind, dass es so ist.
 Der Vorsitzende des SPD-Unterbezirks Essen, der nordrhein-westfälische Justizminister </t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zugewiesen</t>
+  </si>
+  <si>
+    <t>Gestrigen</t>
+  </si>
+  <si>
+    <t>ehrenamtliches Engagement</t>
   </si>
 </sst>
 </file>
@@ -387,15 +386,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1649CCA2-5AFC-4E27-B7F7-FC8D5303FA3F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="364" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -414,7 +423,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="350" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -433,7 +442,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="252" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
